--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0001.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} bất kỳ đâu để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} bất kỳ đâu để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Resonator Skill</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Thu thập 1.200 Phiếu Lollo để mở khóa phần thưởng Phantom</t>
+          <t>Thu thập 1.200 Lollo Vouchers để mở khóa phần thưởng Phantom</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Mới</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Increase</t>
+          <t>Tăng</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
